--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/4161-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/4161-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3F8F1F6-BF6C-4A90-A68A-62DF411F43EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B3C6752-8DCE-450E-93FF-84D780A6FE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{34200BA7-2C00-4E32-90AA-5F21371B1BD4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{29781AAB-8C08-4700-B41E-DBF31441CB32}"/>
   </bookViews>
   <sheets>
     <sheet name="4161-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1448,21 +1448,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27EF361-A204-4E9F-BE6E-C6325B27B194}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E02A5A73-5B1D-440B-AD08-BAF1E7338959}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1616,7 +1616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>2024</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>2023</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2022</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>2021</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>25</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2020</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>25</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>25</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2019</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2018</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2017</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2016</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2015</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2014</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2013</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2012</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2011</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>35</v>
       </c>
